--- a/data/trans_orig/P45C_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P45C_R2-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2007</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2007 (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95808</t>
+          <t>95488</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>134426</t>
+          <t>135720</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51367</t>
+          <t>51105</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80777</t>
+          <t>79580</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>153230</t>
+          <t>155521</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>203861</t>
+          <t>205673</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>558568</t>
+          <t>557274</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>597186</t>
+          <t>597506</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>607574</t>
+          <t>608771</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>636984</t>
+          <t>637246</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1177484</t>
+          <t>1175672</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1228115</t>
+          <t>1225824</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,74%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>135778</t>
+          <t>136111</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>184281</t>
+          <t>185156</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>93623</t>
+          <t>93570</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>134694</t>
+          <t>133094</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>243335</t>
+          <t>242781</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>305192</t>
+          <t>303195</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>774247</t>
+          <t>773372</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>822750</t>
+          <t>822417</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>830168</t>
+          <t>831768</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>871239</t>
+          <t>871292</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1618199</t>
+          <t>1620196</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1680056</t>
+          <t>1680610</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,38%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81865</t>
+          <t>81516</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>119121</t>
+          <t>119709</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>83092</t>
+          <t>82103</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>118718</t>
+          <t>117282</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>172826</t>
+          <t>173977</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>222837</t>
+          <t>226524</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>558576</t>
+          <t>557988</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>595832</t>
+          <t>596181</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>563462</t>
+          <t>564898</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>599088</t>
+          <t>600077</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1137040</t>
+          <t>1133353</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1187051</t>
+          <t>1185900</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,21%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>121824</t>
+          <t>121578</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>162700</t>
+          <t>162578</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>122388</t>
+          <t>121332</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>166239</t>
+          <t>165025</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>254258</t>
+          <t>253968</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>315365</t>
+          <t>315810</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>776945</t>
+          <t>777067</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>817821</t>
+          <t>818067</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>869367</t>
+          <t>870581</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>913218</t>
+          <t>914274</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1659886</t>
+          <t>1659441</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1720993</t>
+          <t>1721283</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,14%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>470835</t>
+          <t>471293</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>553488</t>
+          <t>558570</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>380482</t>
+          <t>384174</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>456084</t>
+          <t>457603</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>873613</t>
+          <t>873195</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>990516</t>
+          <t>991115</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2715376</t>
+          <t>2710294</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2798029</t>
+          <t>2797571</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2914915</t>
+          <t>2913396</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2990517</t>
+          <t>2986825</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5649348</t>
+          <t>5648749</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5766251</t>
+          <t>5766669</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,85%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2012</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2012 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>104366</t>
+          <t>106344</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>144081</t>
+          <t>146377</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>76114</t>
+          <t>76489</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>116293</t>
+          <t>112884</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>191732</t>
+          <t>192982</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>247963</t>
+          <t>246842</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>553735</t>
+          <t>551439</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>593450</t>
+          <t>591472</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>578669</t>
+          <t>582078</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>618848</t>
+          <t>618473</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1144814</t>
+          <t>1145935</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1201045</t>
+          <t>1199795</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,14%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>138637</t>
+          <t>139162</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>188197</t>
+          <t>183755</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>110344</t>
+          <t>111152</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>154326</t>
+          <t>151708</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>261074</t>
+          <t>260209</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>323447</t>
+          <t>326616</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>819868</t>
+          <t>824310</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>869428</t>
+          <t>868903</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>866823</t>
+          <t>869441</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>910805</t>
+          <t>909997</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1705767</t>
+          <t>1702598</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1768140</t>
+          <t>1769005</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,18%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>115328</t>
+          <t>113218</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>158882</t>
+          <t>157457</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>89992</t>
+          <t>90818</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130385</t>
+          <t>130259</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>216624</t>
+          <t>215745</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>274555</t>
+          <t>274204</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>590439</t>
+          <t>591864</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>633993</t>
+          <t>636103</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>637242</t>
+          <t>637368</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>677635</t>
+          <t>676809</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1242394</t>
+          <t>1242745</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1300325</t>
+          <t>1301204</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,78%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>153024</t>
+          <t>154488</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>203352</t>
+          <t>204200</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120160</t>
+          <t>121094</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>164272</t>
+          <t>164524</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>286358</t>
+          <t>284993</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>349594</t>
+          <t>348694</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>740493</t>
+          <t>739645</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>790821</t>
+          <t>789357</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>875418</t>
+          <t>875166</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>919530</t>
+          <t>918596</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1633941</t>
+          <t>1634841</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1697177</t>
+          <t>1698542</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,63%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>553901</t>
+          <t>551193</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>642646</t>
+          <t>641753</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>430882</t>
+          <t>431953</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>516401</t>
+          <t>515392</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1015275</t>
+          <t>1012265</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1135391</t>
+          <t>1136203</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2756401</t>
+          <t>2757294</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2845146</t>
+          <t>2847854</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3007026</t>
+          <t>3008035</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3092545</t>
+          <t>3091474</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5787084</t>
+          <t>5786272</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5907200</t>
+          <t>5910210</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,38%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2016</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2016 (tasa de respuesta: 99,24%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41204</t>
+          <t>40767</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72199</t>
+          <t>69399</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39412</t>
+          <t>39638</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66986</t>
+          <t>66906</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>86668</t>
+          <t>87624</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>124880</t>
+          <t>126653</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>600621</t>
+          <t>603421</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>631616</t>
+          <t>632053</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>603045</t>
+          <t>603125</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>630619</t>
+          <t>630393</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1217971</t>
+          <t>1216198</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1256183</t>
+          <t>1255227</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>111159</t>
+          <t>110065</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>155785</t>
+          <t>157054</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>105443</t>
+          <t>106762</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>147807</t>
+          <t>148778</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>225285</t>
+          <t>224303</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>288282</t>
+          <t>287786</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>856858</t>
+          <t>855589</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>901484</t>
+          <t>902578</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>888569</t>
+          <t>887598</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>930933</t>
+          <t>929614</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1760737</t>
+          <t>1761233</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1823734</t>
+          <t>1824716</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,05%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97212</t>
+          <t>97814</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>137734</t>
+          <t>138827</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>120184</t>
+          <t>117966</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>163382</t>
+          <t>164689</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>227102</t>
+          <t>229303</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>287625</t>
+          <t>288005</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>611405</t>
+          <t>610312</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>651927</t>
+          <t>651325</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>612154</t>
+          <t>610847</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>655352</t>
+          <t>657570</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1237050</t>
+          <t>1236670</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1297573</t>
+          <t>1295372</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,96%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>131010</t>
+          <t>130020</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>174711</t>
+          <t>176210</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>137279</t>
+          <t>137252</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>184232</t>
+          <t>182085</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>279454</t>
+          <t>278853</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>341746</t>
+          <t>345181</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,55%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>755959</t>
+          <t>754460</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>799660</t>
+          <t>800650</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>852033</t>
+          <t>854180</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>898986</t>
+          <t>899013</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1625189</t>
+          <t>1621754</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1687481</t>
+          <t>1688082</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,82%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>417035</t>
+          <t>411298</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>500918</t>
+          <t>496714</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,47 +6014,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>12,22%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>14,76%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>477446</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>436026</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>517030</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>13,57%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>12,39%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>14,88%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>463</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>477446</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>437175</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>516935</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>13,57%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>12,43%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>870594</t>
+          <t>876401</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>993009</t>
+          <t>986589</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2864354</t>
+          <t>2868558</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2948237</t>
+          <t>2953974</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,49 +6127,49 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>87,78%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3040762</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3001178</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3082182</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>86,43%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>85,3%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
           <t>87,61%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2852</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3040762</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>3001273</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3081033</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>86,43%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>85,31%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>87,57%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>5633</t>
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5890471</t>
+          <t>5896891</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6012886</t>
+          <t>6007079</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,27%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2023</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>113463</t>
+          <t>113177</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>168211</t>
+          <t>170391</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>99155</t>
+          <t>99546</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>132285</t>
+          <t>130876</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>223742</t>
+          <t>220158</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>289497</t>
+          <t>285178</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>463488</t>
+          <t>461308</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>518236</t>
+          <t>518522</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>542536</t>
+          <t>543945</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>575666</t>
+          <t>575275</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1017024</t>
+          <t>1021343</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1082779</t>
+          <t>1086363</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,15%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69804</t>
+          <t>68138</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>183901</t>
+          <t>186489</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>123811</t>
+          <t>123589</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>163870</t>
+          <t>164503</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>194653</t>
+          <t>187810</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>327356</t>
+          <t>328787</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1007836</t>
+          <t>1005248</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1121933</t>
+          <t>1123599</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>793576</t>
+          <t>792943</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>833635</t>
+          <t>833857</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1821827</t>
+          <t>1820396</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1954530</t>
+          <t>1961373</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,26%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>105120</t>
+          <t>102936</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155644</t>
+          <t>156120</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43928</t>
+          <t>45214</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>124246</t>
+          <t>127895</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>134393</t>
+          <t>138842</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>268358</t>
+          <t>266283</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>546618</t>
+          <t>546142</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>597142</t>
+          <t>599326</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>808365</t>
+          <t>804716</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>888683</t>
+          <t>887397</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1366515</t>
+          <t>1368590</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1500480</t>
+          <t>1496031</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,51%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>108916</t>
+          <t>107634</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>156715</t>
+          <t>155128</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78558</t>
+          <t>80122</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123761</t>
+          <t>123775</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>197357</t>
+          <t>196681</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>265548</t>
+          <t>261732</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>770116</t>
+          <t>771703</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>817915</t>
+          <t>819197</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>970481</t>
+          <t>970467</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1015684</t>
+          <t>1014120</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1755525</t>
+          <t>1759341</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1823716</t>
+          <t>1824392</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,27%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>427918</t>
+          <t>415959</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>596289</t>
+          <t>602016</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>371769</t>
+          <t>367559</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>501114</t>
+          <t>499047</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>856184</t>
+          <t>850031</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1066815</t>
+          <t>1071214</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2856241</t>
+          <t>2850514</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3024612</t>
+          <t>3036571</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3158006</t>
+          <t>3160073</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3287351</t>
+          <t>3291561</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6044835</t>
+          <t>6040436</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6255466</t>
+          <t>6261619</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P45C_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P45C_R2-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95488</t>
+          <t>93927</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>135720</t>
+          <t>134429</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51105</t>
+          <t>51660</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79580</t>
+          <t>80637</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>155521</t>
+          <t>156553</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>205673</t>
+          <t>201573</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>557274</t>
+          <t>558565</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>597506</t>
+          <t>599067</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>608771</t>
+          <t>607714</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>637246</t>
+          <t>636691</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1175672</t>
+          <t>1179772</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1225824</t>
+          <t>1224792</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,67%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>136111</t>
+          <t>136805</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>185156</t>
+          <t>183741</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>93570</t>
+          <t>94368</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>133094</t>
+          <t>135083</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>242781</t>
+          <t>241399</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>303195</t>
+          <t>301688</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>773372</t>
+          <t>774787</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>822417</t>
+          <t>821723</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>831768</t>
+          <t>829779</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>871292</t>
+          <t>870494</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1620196</t>
+          <t>1621703</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1680610</t>
+          <t>1681992</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,45%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81516</t>
+          <t>80283</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>119709</t>
+          <t>118539</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82103</t>
+          <t>81491</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>117282</t>
+          <t>117730</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>173977</t>
+          <t>172578</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>226524</t>
+          <t>223798</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>557988</t>
+          <t>559158</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>596181</t>
+          <t>597414</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>564898</t>
+          <t>564450</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>600077</t>
+          <t>600689</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1133353</t>
+          <t>1136079</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1185900</t>
+          <t>1187299</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,31%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>121578</t>
+          <t>121814</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>162588</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>121332</t>
+          <t>120998</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>165025</t>
+          <t>167445</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>253968</t>
+          <t>254521</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>315810</t>
+          <t>315643</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>777067</t>
+          <t>777057</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>818067</t>
+          <t>817831</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>870581</t>
+          <t>868161</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>914274</t>
+          <t>914608</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1659441</t>
+          <t>1659608</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1721283</t>
+          <t>1720730</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,11%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>471293</t>
+          <t>472239</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>558570</t>
+          <t>557285</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>384174</t>
+          <t>380718</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>457603</t>
+          <t>459893</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>873195</t>
+          <t>880119</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>991115</t>
+          <t>988972</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2710294</t>
+          <t>2711579</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2797571</t>
+          <t>2796625</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2913396</t>
+          <t>2911106</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2986825</t>
+          <t>2990281</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5648749</t>
+          <t>5650892</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5766669</t>
+          <t>5759745</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,74%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>106344</t>
+          <t>104932</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>146377</t>
+          <t>146482</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>76489</t>
+          <t>75823</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>112884</t>
+          <t>113719</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>192982</t>
+          <t>193852</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>246842</t>
+          <t>248952</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>551439</t>
+          <t>551334</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>591472</t>
+          <t>592884</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>582078</t>
+          <t>581243</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>618473</t>
+          <t>619139</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1145935</t>
+          <t>1143825</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1199795</t>
+          <t>1198925</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,08%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>139162</t>
+          <t>137876</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>183755</t>
+          <t>185650</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>111152</t>
+          <t>110517</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>151708</t>
+          <t>154543</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>260209</t>
+          <t>260592</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>326616</t>
+          <t>324997</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,02%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>824310</t>
+          <t>822415</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>868903</t>
+          <t>870189</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>869441</t>
+          <t>866606</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>909997</t>
+          <t>910632</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1702598</t>
+          <t>1704217</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1769005</t>
+          <t>1768622</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113218</t>
+          <t>115940</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>157457</t>
+          <t>160565</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90818</t>
+          <t>88588</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130259</t>
+          <t>127198</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>215745</t>
+          <t>218708</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>274204</t>
+          <t>277382</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>591864</t>
+          <t>588756</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>636103</t>
+          <t>633381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>637368</t>
+          <t>640429</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>676809</t>
+          <t>679039</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1242745</t>
+          <t>1239567</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1301204</t>
+          <t>1298241</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,58%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>154488</t>
+          <t>156578</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>204200</t>
+          <t>203079</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>121094</t>
+          <t>118581</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>164524</t>
+          <t>163553</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>284993</t>
+          <t>285561</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>348694</t>
+          <t>350179</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>739645</t>
+          <t>740766</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>789357</t>
+          <t>787267</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>875166</t>
+          <t>876137</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>918596</t>
+          <t>921109</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1634841</t>
+          <t>1633356</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1698542</t>
+          <t>1697974</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,6%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>551193</t>
+          <t>551494</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>641753</t>
+          <t>643560</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>431953</t>
+          <t>438102</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>515392</t>
+          <t>517413</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1012265</t>
+          <t>1012196</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1136203</t>
+          <t>1131831</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2757294</t>
+          <t>2755487</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2847854</t>
+          <t>2847553</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3008035</t>
+          <t>3006014</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3091474</t>
+          <t>3085325</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5786272</t>
+          <t>5790644</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5910210</t>
+          <t>5910279</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40767</t>
+          <t>41061</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69399</t>
+          <t>72002</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39638</t>
+          <t>39214</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66906</t>
+          <t>65731</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>87624</t>
+          <t>87816</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>126653</t>
+          <t>126290</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>603421</t>
+          <t>600818</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>632053</t>
+          <t>631759</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>603125</t>
+          <t>604300</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>630393</t>
+          <t>630817</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1216198</t>
+          <t>1216561</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1255227</t>
+          <t>1255035</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,46%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>110065</t>
+          <t>109197</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>157054</t>
+          <t>156503</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>106762</t>
+          <t>105776</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>148778</t>
+          <t>148978</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>224303</t>
+          <t>229794</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>287786</t>
+          <t>290767</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>855589</t>
+          <t>856140</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>902578</t>
+          <t>903446</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>887598</t>
+          <t>887398</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>929614</t>
+          <t>930600</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1761233</t>
+          <t>1758252</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1824716</t>
+          <t>1819225</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,79%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97814</t>
+          <t>97447</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>138827</t>
+          <t>138063</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>117966</t>
+          <t>119922</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>164689</t>
+          <t>164990</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>229303</t>
+          <t>228131</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>288005</t>
+          <t>290011</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,02%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>610312</t>
+          <t>611076</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>651325</t>
+          <t>651692</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>610847</t>
+          <t>610546</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>657570</t>
+          <t>655614</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1236670</t>
+          <t>1234664</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1295372</t>
+          <t>1296544</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,04%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>130020</t>
+          <t>128221</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>176210</t>
+          <t>172365</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>137252</t>
+          <t>137131</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>182085</t>
+          <t>185223</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>278853</t>
+          <t>279603</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>345181</t>
+          <t>343059</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>754460</t>
+          <t>758305</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>800650</t>
+          <t>802449</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>854180</t>
+          <t>851042</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>899013</t>
+          <t>899134</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1621754</t>
+          <t>1623876</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1688082</t>
+          <t>1687332</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,78%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>411298</t>
+          <t>411999</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>496714</t>
+          <t>493086</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>436026</t>
+          <t>437319</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>517030</t>
+          <t>520957</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>876401</t>
+          <t>876199</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>986589</t>
+          <t>990913</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2868558</t>
+          <t>2872186</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2953974</t>
+          <t>2953273</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3001178</t>
+          <t>2997251</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3082182</t>
+          <t>3080889</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5896891</t>
+          <t>5892567</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6007079</t>
+          <t>6007281</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>136892</t>
+          <t>147823</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>113177</t>
+          <t>125101</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>170391</t>
+          <t>174959</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>114482</t>
+          <t>121905</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>99546</t>
+          <t>104510</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>130876</t>
+          <t>138931</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>251375</t>
+          <t>269728</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>220158</t>
+          <t>240335</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>285178</t>
+          <t>303117</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>494807</t>
+          <t>538986</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>461308</t>
+          <t>511850</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>518522</t>
+          <t>561708</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>560339</t>
+          <t>610180</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>543945</t>
+          <t>593154</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>575275</t>
+          <t>627575</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1055146</t>
+          <t>1149166</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1021343</t>
+          <t>1115777</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1086363</t>
+          <t>1178559</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,06%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>631699</t>
+          <t>686809</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>631699</t>
+          <t>686809</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>631699</t>
+          <t>686809</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>674821</t>
+          <t>732085</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>674821</t>
+          <t>732085</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>674821</t>
+          <t>732085</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1306521</t>
+          <t>1418894</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1306521</t>
+          <t>1418894</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1306521</t>
+          <t>1418894</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>137250</t>
+          <t>158575</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68138</t>
+          <t>131610</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>186489</t>
+          <t>187540</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>142352</t>
+          <t>155962</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>123589</t>
+          <t>137457</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>164503</t>
+          <t>177562</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>279602</t>
+          <t>314537</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>187810</t>
+          <t>278828</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>328787</t>
+          <t>350642</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1054487</t>
+          <t>889154</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1005248</t>
+          <t>860189</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1123599</t>
+          <t>916119</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>815094</t>
+          <t>914116</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>792943</t>
+          <t>892516</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>833857</t>
+          <t>932621</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1869581</t>
+          <t>1803270</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1820396</t>
+          <t>1767165</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1961373</t>
+          <t>1838979</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>86,83%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1191737</t>
+          <t>1047729</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1191737</t>
+          <t>1047729</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1191737</t>
+          <t>1047729</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957446</t>
+          <t>1070078</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957446</t>
+          <t>1070078</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957446</t>
+          <t>1070078</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2149183</t>
+          <t>2117807</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2149183</t>
+          <t>2117807</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2149183</t>
+          <t>2117807</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>128663</t>
+          <t>148408</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>102936</t>
+          <t>122724</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>156120</t>
+          <t>176687</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>92016</t>
+          <t>108276</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45214</t>
+          <t>91783</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>127895</t>
+          <t>129840</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>220679</t>
+          <t>256684</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138842</t>
+          <t>224804</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>266283</t>
+          <t>289902</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>573599</t>
+          <t>652259</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>546142</t>
+          <t>623980</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>599326</t>
+          <t>677943</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>840595</t>
+          <t>701936</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>804716</t>
+          <t>680372</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>887397</t>
+          <t>718429</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1414194</t>
+          <t>1354195</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1368590</t>
+          <t>1320977</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1496031</t>
+          <t>1386075</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>86,04%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>702262</t>
+          <t>800667</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>702262</t>
+          <t>800667</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>702262</t>
+          <t>800667</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932611</t>
+          <t>810212</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932611</t>
+          <t>810212</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932611</t>
+          <t>810212</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1634873</t>
+          <t>1610879</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1634873</t>
+          <t>1610879</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1634873</t>
+          <t>1610879</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>129211</t>
+          <t>143393</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>107634</t>
+          <t>121159</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>155128</t>
+          <t>170212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>101593</t>
+          <t>111245</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80122</t>
+          <t>91854</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123775</t>
+          <t>133173</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>230803</t>
+          <t>254638</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>196681</t>
+          <t>222697</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>261732</t>
+          <t>287913</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>797620</t>
+          <t>846669</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>771703</t>
+          <t>819850</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>819197</t>
+          <t>868903</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>992649</t>
+          <t>1007038</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>970467</t>
+          <t>985110</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1014120</t>
+          <t>1026429</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1790270</t>
+          <t>1853707</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1759341</t>
+          <t>1820432</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1824392</t>
+          <t>1885648</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>89,44%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094242</t>
+          <t>1118283</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094242</t>
+          <t>1118283</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094242</t>
+          <t>1118283</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021073</t>
+          <t>2108345</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021073</t>
+          <t>2108345</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021073</t>
+          <t>2108345</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>532017</t>
+          <t>598199</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>415959</t>
+          <t>546737</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>602016</t>
+          <t>656550</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>450443</t>
+          <t>497389</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>367559</t>
+          <t>459725</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>499047</t>
+          <t>538703</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>982460</t>
+          <t>1095588</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>850031</t>
+          <t>1034481</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1071214</t>
+          <t>1166270</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2920513</t>
+          <t>2927068</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2850514</t>
+          <t>2868717</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3036571</t>
+          <t>2978530</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3208677</t>
+          <t>3233269</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3160073</t>
+          <t>3191955</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3291561</t>
+          <t>3270933</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6129190</t>
+          <t>6160337</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6040436</t>
+          <t>6089655</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6261619</t>
+          <t>6221444</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>85,74%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3452530</t>
+          <t>3525267</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3452530</t>
+          <t>3525267</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3452530</t>
+          <t>3525267</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3659120</t>
+          <t>3730658</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3659120</t>
+          <t>3730658</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3659120</t>
+          <t>3730658</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7111650</t>
+          <t>7255925</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7111650</t>
+          <t>7255925</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7111650</t>
+          <t>7255925</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
